--- a/Data/异常值报告.xlsx
+++ b/Data/异常值报告.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3275,6 +3275,103 @@
         </is>
       </c>
       <c r="U31" t="inlineStr">
+        <is>
+          <t>转门诊</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>骨十一科</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>程建英</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0001008673</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>71岁</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>^</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>股骨内固定装置去除术</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>张昕</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2024-12-17 16:39:25</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>407737</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024-12-18 09:20:22</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>骨十一科</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 </t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>3401.36</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>转门诊</t>
         </is>
@@ -3825,7 +3922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4440,6 +4537,302 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>转住院</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>白景奎</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0001171090</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>76岁</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>冠状动脉粥样硬化性心脏病*冠状动脉粥样硬化性心脏病^I25.103</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>经皮穿刺脊柱后凸成形术</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>贾丁丁</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2024-12-17 08:45:13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>周立宾</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>399601</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024-12-18 10:16:55</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>内二科</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>14595.61</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>转住院</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>骨二科</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>赵景联</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0001261471</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72岁</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>膝关节病*左膝关节病^M17.900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>侯心昕</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2024-12-21 08:14:02</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>王燕</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>407939</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024-12-22 08:25:58</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>呼吸与危重症医学科</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>8712.51</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>转住院</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>王三香</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0001198901</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>68岁</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>脊柱内固定装置障碍*脊柱畸形术后内植物失效^T84.202</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2024-12-16</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>郝运兵</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2024-12-23 07:58:37</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>田忠</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>407641</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024-12-23 14:27:33</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>重症医学科</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>16497.05</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>转住院</t>
         </is>
@@ -5192,7 +5585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5270,6 +5663,81 @@
         <is>
           <t>住院天数数字</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>程建英</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>407737</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>71岁</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>还未办理</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>股骨内固定装置去除术</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2024-12-17 14:50:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>骨十一科</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>骨十一科</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2024-12-18 08:44:54</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3401.36</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6097,7 +6565,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -6107,7 +6575,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10578.17</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -6570,7 +7038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13475,6 +13943,831 @@
         <v>2</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>王记枝</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>406963</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>74岁</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>王少锋</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>经皮椎体球囊扩张成形术</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2024-12-06 09:17:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2024-12-08 08:16:46</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>13562.63</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>吴秋玲</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>395210</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>64岁</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>张梦鑫</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>经皮穿刺脊柱后凸成形术</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2024-12-09 09:55:00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2024-12-10 15:04:04</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>10893.67</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>李书金</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>407178</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>81岁</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>杨克</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>经皮椎骨成形术</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2024-12-09 10:47:00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:59:42</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>15741.84</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>王小英</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>407217</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>65岁</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>王少锋</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>经皮椎体球囊扩张成形术</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2024-12-09 15:44:00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2024-12-11 09:16:41</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>13134.47</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>史素腔</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>407289</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>66岁</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>吴华荣</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>经皮穿刺脊柱后凸成形术</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2024-12-10 17:36:00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>骨六科</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>骨六科</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2024-12-12 09:37:16</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>12520.74</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>吉香果</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>407582</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>64岁</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>张尚普</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>关节镜膝关节半月板切除术</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2024-12-17 09:57:00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>骨七科</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>骨七科</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2024-12-18 10:16:55</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>12967.21</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>王淑芹</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>407654</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>76岁</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>张梦鑫</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>经皮穿刺脊柱后凸成形术</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2024-12-16 14:37:00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2024-12-17 14:40:36</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>11941.67</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>霍分的</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>407938</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>77岁</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>王少锋</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>经皮椎体球囊扩张成形术</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2024-12-21 08:17:00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2024-12-22 08:25:58</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>13444.03</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>杨花荣</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>407955</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>88岁</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>郝运兵</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>经皮穿刺脊柱后凸成形术</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2024-12-20 17:31:00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2024-12-22 08:40:53</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>12365.24</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>崔平文</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>408120</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>73岁</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>杨克</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>经皮椎骨成形术</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2024-12-23 11:04:00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>骨九科</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2024-12-25 10:22:13</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>13847.66</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>张宋芹</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>408145</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>62岁</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>王学攀</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>经皮穿刺脊柱后凸成形术</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2024-12-23 14:43:00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>骨一科</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>骨一科</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2024-12-25 10:07:04</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>12131.13</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>门诊</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
